--- a/out/Petra Speech Logs 2025-06 June_cleaned.xlsx
+++ b/out/Petra Speech Logs 2025-06 June_cleaned.xlsx
@@ -473,9 +473,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="65" customWidth="1" min="7" max="7"/>
@@ -493,17 +493,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Week of (Monday)</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>Date of Service</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Day of Week</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Week of (Monday)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -550,17 +550,17 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>06/03/2025</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>06/02/2025</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -571,7 +571,7 @@
       <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>End time: 9:45  am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -603,19 +603,19 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>06/03/2025</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>06/02/2025</t>
-        </is>
-      </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Start 9:30am - End 10:00am</t>
@@ -628,7 +628,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>End time: 10:00 am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -660,19 +660,19 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
+          <t>06/02/2025</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
           <t>06/03/2025</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06/02/2025</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Start 10:00am - End 10:30am</t>
@@ -685,7 +685,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>End time: 10:30 am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -717,19 +717,19 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>06/10/2025</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06/09/2025</t>
-        </is>
-      </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Start 9:30am - End 10:00am</t>
@@ -742,7 +742,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>End time: 10:00 am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -774,19 +774,19 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
+          <t>06/09/2025</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
           <t>06/10/2025</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tuesday</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>06/09/2025</t>
-        </is>
-      </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Start 10:00am - End 10:30am</t>
@@ -799,7 +799,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>End time: 10:30 am Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
+          <t>Speech &amp; Language (Receptive): Given initial models, gestural cues, clear and concise expectations, multisensory cues and a fading prompt hierarchy, Petra will follow single-step directions including spatial concepts and pronouns with 80% accuracy in 4 out of 5 observed opportunities across 3 sessions by May 2025. Speech &amp; Language (Expressive): Given wait time and no more than an initial model and two gestural cues, Petra will increase utterance length using multimodal communication tools (i.e. gestures/signs, pictures/picture symbols, words/word approximations, voice output devices, speech generating devices) for 2+ words to make comments, requests, protests, and answer questions in 4 out of 5 opportunities across three sessions by May 2025.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
